--- a/backtest_runs/20260410_193731/by_symbol/SIBL/SIBL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SIBL/SIBL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-540.5600000000005</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>99459.44</v>
@@ -679,7 +679,7 @@
         <v>-13514</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>85945.44</v>
@@ -771,7 +771,7 @@
         <v>-135.1399999999971</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>85810.3</v>
@@ -863,7 +863,7 @@
         <v>-9054.379999999999</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>76755.92</v>
@@ -909,7 +909,7 @@
         <v>-7297.56</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>69458.36</v>
@@ -1047,7 +1047,7 @@
         <v>-270.2799999999942</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>69188.08</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>72566.58</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>72566.58</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>72566.58</v>
